--- a/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-stresstype-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-stresstype-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationElectrogardiogramStressType_CS</t>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationElectrocardiogramStressType_CS</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>JP_ObservationElectrogardiogramStressType_CS</t>
+    <t>JP_ObservationElectrocardiogramStressType_CS</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>JP Core Observation ElectroCardioGram StressType CodeSystem</t>
+    <t>JP Core Observation Electrocardiogram StressType CodeSystem</t>
   </si>
   <si>
     <t>Status</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>Level</t>
@@ -144,34 +144,55 @@
     <t>1</t>
   </si>
   <si>
+    <t>JECGST0000</t>
+  </si>
+  <si>
+    <t>安静時</t>
+  </si>
+  <si>
     <t>JECGST0100</t>
   </si>
   <si>
     <t>SM</t>
   </si>
   <si>
+    <t>Single Master</t>
+  </si>
+  <si>
     <t>JECGST0200</t>
   </si>
   <si>
     <t>DM</t>
   </si>
   <si>
+    <t>Double Master</t>
+  </si>
+  <si>
     <t>JECGST0300</t>
   </si>
   <si>
     <t>TM</t>
   </si>
   <si>
+    <t>Triple Master</t>
+  </si>
+  <si>
     <t>JECGST0400</t>
   </si>
   <si>
     <t>1/2</t>
   </si>
   <si>
+    <t>1/2 Master</t>
+  </si>
+  <si>
     <t>JECGST0500</t>
   </si>
   <si>
     <t>1/4</t>
+  </si>
+  <si>
+    <t>1/4 Master</t>
   </si>
   <si>
     <t>JECGST0600</t>
@@ -525,7 +546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -564,65 +585,75 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>53</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>59</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -631,10 +662,10 @@
         <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -643,10 +674,10 @@
         <v>42</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -655,10 +686,10 @@
         <v>42</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -667,10 +698,10 @@
         <v>42</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -679,12 +710,24 @@
         <v>42</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D14" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-stresstype-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-stresstype-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-stresstype-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-stresstype-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-stresstype-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-stresstype-cs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>Case Sensitive</t>
